--- a/test_plan.xlsx
+++ b/test_plan.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OMEN\Documents\Eng. Raghad\DV\Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OMEN\Documents\Eng. Raghad\DV\DV_project-claude-busy-turing-q1vwei\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F679C8-7966-4A48-9252-6E27D5A71B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD10F78B-B97A-40B6-BE31-1358EC5A83E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{2A3F12D1-36D3-4428-BC65-043ACAAD9E53}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{2A3F12D1-36D3-4428-BC65-043ACAAD9E53}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="320">
   <si>
     <t>Electrical and Computer Engineering Department</t>
   </si>
@@ -980,13 +980,19 @@
   </si>
   <si>
     <t>ADDITIONAL CFG &amp; REMOTE VALIDATION</t>
+  </si>
+  <si>
+    <t>Run</t>
+  </si>
+  <si>
+    <t>Run with error</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1050,8 +1056,36 @@
       <color rgb="FFE36C09"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1088,6 +1122,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDEEAF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1188,10 +1232,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
+      <left style="thin">
         <color rgb="FFB8CCE4"/>
-      </right>
+      </left>
+      <right/>
       <top style="thin">
         <color rgb="FFB8CCE4"/>
       </top>
@@ -1201,16 +1245,64 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1253,45 +1345,19 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Bad" xfId="2" builtinId="27"/>
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1681,18 +1747,18 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="20"/>
+      <c r="S3" s="20"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
@@ -1715,16 +1781,16 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
@@ -1747,18 +1813,18 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
@@ -1781,16 +1847,16 @@
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
@@ -1813,18 +1879,18 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
@@ -1847,16 +1913,16 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="20"/>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
@@ -1879,18 +1945,18 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
@@ -2009,18 +2075,18 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
-      <c r="S13" s="6"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
@@ -2043,16 +2109,16 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="6"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="20"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
@@ -2075,18 +2141,18 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="6" t="s">
+      <c r="J15" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="6"/>
-      <c r="S15" s="6"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="20"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
@@ -2109,16 +2175,16 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
-      <c r="S16" s="6"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="20"/>
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
@@ -2141,18 +2207,18 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="6" t="s">
+      <c r="J17" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="6"/>
-      <c r="R17" s="6"/>
-      <c r="S17" s="6"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="20"/>
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
@@ -2175,16 +2241,16 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="20"/>
+      <c r="S18" s="20"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
@@ -2207,18 +2273,18 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="19" t="s">
+      <c r="J19" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="P19" s="19"/>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="19"/>
-      <c r="S19" s="19"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="33"/>
+      <c r="N19" s="33"/>
+      <c r="O19" s="33"/>
+      <c r="P19" s="33"/>
+      <c r="Q19" s="33"/>
+      <c r="R19" s="33"/>
+      <c r="S19" s="33"/>
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
@@ -2241,16 +2307,16 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="19"/>
-      <c r="S20" s="19"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="33"/>
+      <c r="N20" s="33"/>
+      <c r="O20" s="33"/>
+      <c r="P20" s="33"/>
+      <c r="Q20" s="33"/>
+      <c r="R20" s="33"/>
+      <c r="S20" s="33"/>
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
@@ -2273,16 +2339,16 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
-      <c r="S21" s="19"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="33"/>
+      <c r="P21" s="33"/>
+      <c r="Q21" s="33"/>
+      <c r="R21" s="33"/>
+      <c r="S21" s="33"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
@@ -2305,16 +2371,16 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="19"/>
-      <c r="S22" s="19"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+      <c r="N22" s="33"/>
+      <c r="O22" s="33"/>
+      <c r="P22" s="33"/>
+      <c r="Q22" s="33"/>
+      <c r="R22" s="33"/>
+      <c r="S22" s="33"/>
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
@@ -2465,18 +2531,18 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="6" t="s">
+      <c r="J27" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="6"/>
-      <c r="S27" s="6"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20"/>
+      <c r="R27" s="20"/>
+      <c r="S27" s="20"/>
       <c r="T27" s="1"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
@@ -2499,16 +2565,16 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="6"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="20"/>
+      <c r="S28" s="20"/>
       <c r="T28" s="1"/>
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
@@ -2531,22 +2597,22 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="13" t="s">
+      <c r="J29" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="14"/>
-      <c r="P29" s="13" t="s">
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="28"/>
+      <c r="P29" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="Q29" s="14"/>
-      <c r="R29" s="13" t="s">
+      <c r="Q29" s="28"/>
+      <c r="R29" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="S29" s="14"/>
+      <c r="S29" s="28"/>
       <c r="T29" s="1"/>
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
@@ -2569,16 +2635,16 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="18"/>
-      <c r="M30" s="18"/>
-      <c r="N30" s="18"/>
-      <c r="O30" s="16"/>
-      <c r="P30" s="15"/>
-      <c r="Q30" s="16"/>
-      <c r="R30" s="15"/>
-      <c r="S30" s="16"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="32"/>
+      <c r="L30" s="32"/>
+      <c r="M30" s="32"/>
+      <c r="N30" s="32"/>
+      <c r="O30" s="30"/>
+      <c r="P30" s="29"/>
+      <c r="Q30" s="30"/>
+      <c r="R30" s="29"/>
+      <c r="S30" s="30"/>
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
@@ -2601,22 +2667,22 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
-      <c r="J31" s="7" t="s">
+      <c r="J31" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="11"/>
-      <c r="O31" s="8"/>
-      <c r="P31" s="7">
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="25"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="21">
         <v>1191612</v>
       </c>
-      <c r="Q31" s="8"/>
-      <c r="R31" s="7">
+      <c r="Q31" s="22"/>
+      <c r="R31" s="21">
         <v>2</v>
       </c>
-      <c r="S31" s="8"/>
+      <c r="S31" s="22"/>
       <c r="T31" s="1"/>
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
@@ -2639,16 +2705,16 @@
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="10"/>
-      <c r="P32" s="9"/>
-      <c r="Q32" s="10"/>
-      <c r="R32" s="9"/>
-      <c r="S32" s="10"/>
+      <c r="J32" s="23"/>
+      <c r="K32" s="26"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="26"/>
+      <c r="O32" s="24"/>
+      <c r="P32" s="23"/>
+      <c r="Q32" s="24"/>
+      <c r="R32" s="23"/>
+      <c r="S32" s="24"/>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
@@ -2671,22 +2737,22 @@
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
-      <c r="J33" s="7" t="s">
+      <c r="J33" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
-      <c r="O33" s="8"/>
-      <c r="P33" s="7">
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="25"/>
+      <c r="O33" s="22"/>
+      <c r="P33" s="21">
         <v>1212214</v>
       </c>
-      <c r="Q33" s="8"/>
-      <c r="R33" s="7">
+      <c r="Q33" s="22"/>
+      <c r="R33" s="21">
         <v>1</v>
       </c>
-      <c r="S33" s="8"/>
+      <c r="S33" s="22"/>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
@@ -2709,16 +2775,16 @@
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="12"/>
-      <c r="N34" s="12"/>
-      <c r="O34" s="10"/>
-      <c r="P34" s="9"/>
-      <c r="Q34" s="10"/>
-      <c r="R34" s="9"/>
-      <c r="S34" s="10"/>
+      <c r="J34" s="23"/>
+      <c r="K34" s="26"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="26"/>
+      <c r="O34" s="24"/>
+      <c r="P34" s="23"/>
+      <c r="Q34" s="24"/>
+      <c r="R34" s="23"/>
+      <c r="S34" s="24"/>
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
@@ -2741,22 +2807,22 @@
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
-      <c r="J35" s="7" t="s">
+      <c r="J35" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-      <c r="O35" s="8"/>
-      <c r="P35" s="7">
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
+      <c r="M35" s="25"/>
+      <c r="N35" s="25"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="21">
         <v>1221082</v>
       </c>
-      <c r="Q35" s="8"/>
-      <c r="R35" s="7">
+      <c r="Q35" s="22"/>
+      <c r="R35" s="21">
         <v>1</v>
       </c>
-      <c r="S35" s="8"/>
+      <c r="S35" s="22"/>
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
@@ -2779,16 +2845,16 @@
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="12"/>
-      <c r="M36" s="12"/>
-      <c r="N36" s="12"/>
-      <c r="O36" s="10"/>
-      <c r="P36" s="9"/>
-      <c r="Q36" s="10"/>
-      <c r="R36" s="9"/>
-      <c r="S36" s="10"/>
+      <c r="J36" s="23"/>
+      <c r="K36" s="26"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="26"/>
+      <c r="N36" s="26"/>
+      <c r="O36" s="24"/>
+      <c r="P36" s="23"/>
+      <c r="Q36" s="24"/>
+      <c r="R36" s="23"/>
+      <c r="S36" s="24"/>
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
@@ -2811,22 +2877,22 @@
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
-      <c r="J37" s="7" t="s">
+      <c r="J37" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
-      <c r="O37" s="8"/>
-      <c r="P37" s="7">
+      <c r="K37" s="25"/>
+      <c r="L37" s="25"/>
+      <c r="M37" s="25"/>
+      <c r="N37" s="25"/>
+      <c r="O37" s="22"/>
+      <c r="P37" s="21">
         <v>1222275</v>
       </c>
-      <c r="Q37" s="8"/>
-      <c r="R37" s="7">
+      <c r="Q37" s="22"/>
+      <c r="R37" s="21">
         <v>2</v>
       </c>
-      <c r="S37" s="8"/>
+      <c r="S37" s="22"/>
       <c r="T37" s="3"/>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
@@ -2849,16 +2915,16 @@
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="12"/>
-      <c r="L38" s="12"/>
-      <c r="M38" s="12"/>
-      <c r="N38" s="12"/>
-      <c r="O38" s="10"/>
-      <c r="P38" s="9"/>
-      <c r="Q38" s="10"/>
-      <c r="R38" s="9"/>
-      <c r="S38" s="10"/>
+      <c r="J38" s="23"/>
+      <c r="K38" s="26"/>
+      <c r="L38" s="26"/>
+      <c r="M38" s="26"/>
+      <c r="N38" s="26"/>
+      <c r="O38" s="24"/>
+      <c r="P38" s="23"/>
+      <c r="Q38" s="24"/>
+      <c r="R38" s="23"/>
+      <c r="S38" s="24"/>
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
@@ -2945,18 +3011,18 @@
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
-      <c r="J41" s="6" t="s">
+      <c r="J41" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="K41" s="6"/>
-      <c r="L41" s="6"/>
-      <c r="M41" s="6"/>
-      <c r="N41" s="6"/>
-      <c r="O41" s="6"/>
-      <c r="P41" s="6"/>
-      <c r="Q41" s="6"/>
-      <c r="R41" s="6"/>
-      <c r="S41" s="6"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+      <c r="M41" s="20"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="20"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="20"/>
+      <c r="R41" s="20"/>
+      <c r="S41" s="20"/>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
@@ -2979,16 +3045,16 @@
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6"/>
-      <c r="L42" s="6"/>
-      <c r="M42" s="6"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="6"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="6"/>
-      <c r="S42" s="6"/>
+      <c r="J42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
+      <c r="M42" s="20"/>
+      <c r="N42" s="20"/>
+      <c r="O42" s="20"/>
+      <c r="P42" s="20"/>
+      <c r="Q42" s="20"/>
+      <c r="R42" s="20"/>
+      <c r="S42" s="20"/>
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
@@ -3035,15 +3101,9 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J5:S6"/>
-    <mergeCell ref="J7:S8"/>
-    <mergeCell ref="J3:S4"/>
-    <mergeCell ref="J13:S14"/>
-    <mergeCell ref="J15:S16"/>
     <mergeCell ref="J17:S18"/>
     <mergeCell ref="J19:S22"/>
     <mergeCell ref="J27:S28"/>
-    <mergeCell ref="J9:S9"/>
     <mergeCell ref="J41:S42"/>
     <mergeCell ref="R35:S36"/>
     <mergeCell ref="J37:O38"/>
@@ -3060,6 +3120,12 @@
     <mergeCell ref="P29:Q30"/>
     <mergeCell ref="P31:Q32"/>
     <mergeCell ref="P33:Q34"/>
+    <mergeCell ref="J5:S6"/>
+    <mergeCell ref="J7:S8"/>
+    <mergeCell ref="J3:S4"/>
+    <mergeCell ref="J13:S14"/>
+    <mergeCell ref="J15:S16"/>
+    <mergeCell ref="J9:S9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3074,1713 +3140,1713 @@
     <col min="4" max="4" width="39.5703125" customWidth="1"/>
     <col min="5" max="6" width="30.7109375" customWidth="1"/>
     <col min="7" max="9" width="20.7109375" customWidth="1"/>
-    <col min="10" max="10" width="42.140625" customWidth="1"/>
+    <col min="10" max="11" width="42.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="J1" s="34" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="18" t="s">
         <v>293</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="5"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
     </row>
     <row r="3" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="25" t="s">
+      <c r="H3" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="35" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="36"/>
+    </row>
+    <row r="5" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="35"/>
+    </row>
+    <row r="6" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="36"/>
+    </row>
+    <row r="7" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+    </row>
+    <row r="8" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="35"/>
+    </row>
+    <row r="9" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" s="36"/>
+    </row>
+    <row r="10" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10" s="35"/>
+    </row>
+    <row r="11" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+    </row>
+    <row r="12" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I12" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J12" s="35"/>
+    </row>
+    <row r="13" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="J13" s="36"/>
+    </row>
+    <row r="14" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J14" s="35"/>
+    </row>
+    <row r="15" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="J15" s="36"/>
+    </row>
+    <row r="16" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J16" s="35"/>
+    </row>
+    <row r="17" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+    </row>
+    <row r="18" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="J18" s="35"/>
+    </row>
+    <row r="19" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="J19" s="36"/>
+    </row>
+    <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+    </row>
+    <row r="21" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="J21" s="35" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="J22" s="36"/>
+    </row>
+    <row r="23" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="J23" s="35"/>
+    </row>
+    <row r="24" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="J24" s="36"/>
+    </row>
+    <row r="25" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="J25" s="35"/>
+    </row>
+    <row r="26" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="J26" s="36"/>
+    </row>
+    <row r="27" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H27" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="J27" s="35"/>
+    </row>
+    <row r="28" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="J28" s="36"/>
+    </row>
+    <row r="29" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J29" s="35" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+    </row>
+    <row r="31" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="J31" s="35"/>
+    </row>
+    <row r="32" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H32" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="J32" s="36"/>
+    </row>
+    <row r="33" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="J33" s="35"/>
+    </row>
+    <row r="34" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H34" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="J34" s="36"/>
+    </row>
+    <row r="35" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+    </row>
+    <row r="36" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="J36" s="35"/>
+    </row>
+    <row r="37" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="J37" s="36"/>
+    </row>
+    <row r="38" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="J38" s="35"/>
+    </row>
+    <row r="39" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="H39" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="J39" s="36"/>
+    </row>
+    <row r="40" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="J40" s="35" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="18" t="s">
+        <v>300</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+    </row>
+    <row r="42" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H42" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J42" s="35" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H43" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="J43" s="36" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H44" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="J44" s="35"/>
+    </row>
+    <row r="45" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="G45" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="H45" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="J45" s="36"/>
+    </row>
+    <row r="46" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="18" t="s">
+        <v>316</v>
+      </c>
+      <c r="B46" s="19"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="19"/>
+      <c r="I46" s="19"/>
+      <c r="J46" s="19"/>
+    </row>
+    <row r="47" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H47" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="J47" s="35"/>
+    </row>
+    <row r="48" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H48" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="J48" s="36"/>
+    </row>
+    <row r="49" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H49" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="J49" s="35"/>
+    </row>
+    <row r="50" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H50" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="J50" s="36"/>
+    </row>
+    <row r="51" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="G51" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="J51" s="35" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="G52" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H52" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I52" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="28" t="s">
+      <c r="J52" s="36"/>
+    </row>
+    <row r="53" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="B53" s="19"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="19"/>
+      <c r="F53" s="19"/>
+      <c r="G53" s="19"/>
+      <c r="H53" s="19"/>
+      <c r="I53" s="19"/>
+      <c r="J53" s="19"/>
+    </row>
+    <row r="54" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="G54" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="29" t="s">
+      <c r="H54" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" s="27"/>
-    </row>
-    <row r="5" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>247</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="24" t="s">
+      <c r="I54" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J54" s="35"/>
+    </row>
+    <row r="55" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="G55" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="25" t="s">
+      <c r="H55" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="I5" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="J5" s="23"/>
-    </row>
-    <row r="6" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" s="28" t="s">
+      <c r="I55" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="J55" s="36" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="G56" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="29" t="s">
+      <c r="H56" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" s="27"/>
-    </row>
-    <row r="7" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="5"/>
-    </row>
-    <row r="8" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" s="24" t="s">
+      <c r="I56" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J56" s="35"/>
+    </row>
+    <row r="57" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="B57" s="19"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="19"/>
+      <c r="E57" s="19"/>
+      <c r="F57" s="19"/>
+      <c r="G57" s="19"/>
+      <c r="H57" s="19"/>
+      <c r="I57" s="19"/>
+      <c r="J57" s="19"/>
+    </row>
+    <row r="58" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="G58" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H8" s="25" t="s">
+      <c r="H58" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" s="23"/>
-    </row>
-    <row r="9" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" s="28" t="s">
+      <c r="I58" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="J58" s="35"/>
+    </row>
+    <row r="59" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="G59" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="29" t="s">
+      <c r="H59" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="J9" s="27"/>
-    </row>
-    <row r="10" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10" s="24" t="s">
+      <c r="I59" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="J59" s="36"/>
+    </row>
+    <row r="60" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="B60" s="19"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="19"/>
+      <c r="F60" s="19"/>
+      <c r="G60" s="19"/>
+      <c r="H60" s="19"/>
+      <c r="I60" s="19"/>
+      <c r="J60" s="19"/>
+    </row>
+    <row r="61" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="G61" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H10" s="25" t="s">
+      <c r="H61" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="I10" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="J10" s="23"/>
-    </row>
-    <row r="11" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="5"/>
-    </row>
-    <row r="12" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="25" t="s">
+      <c r="I61" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="J61" s="35" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="G62" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="H62" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="J12" s="23"/>
-    </row>
-    <row r="13" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>253</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="F13" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="G13" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="J13" s="27"/>
-    </row>
-    <row r="14" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="F14" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="G14" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H14" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="J14" s="23"/>
-    </row>
-    <row r="15" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>255</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="E15" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F15" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="G15" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H15" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="J15" s="27"/>
-    </row>
-    <row r="16" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="22" t="s">
-        <v>256</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="F16" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="G16" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="H16" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="J16" s="23"/>
-    </row>
-    <row r="17" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
-        <v>297</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="5"/>
-    </row>
-    <row r="18" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="E18" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="F18" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="G18" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="J18" s="23"/>
-    </row>
-    <row r="19" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="E19" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="F19" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="G19" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H19" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="J19" s="27"/>
-    </row>
-    <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="5"/>
-    </row>
-    <row r="21" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>259</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="F21" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="G21" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="J21" s="23" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>260</v>
-      </c>
-      <c r="C22" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="E22" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="F22" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="G22" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H22" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="J22" s="27"/>
-    </row>
-    <row r="23" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>261</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="F23" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="G23" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H23" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="22" t="s">
+      <c r="I62" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="J23" s="23"/>
-    </row>
-    <row r="24" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="B24" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="C24" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="D24" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="E24" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="F24" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="G24" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H24" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="J24" s="27"/>
-    </row>
-    <row r="25" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="B25" s="22" t="s">
-        <v>263</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="F25" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="G25" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H25" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="J25" s="23"/>
-    </row>
-    <row r="26" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="B26" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="C26" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D26" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="E26" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="F26" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="G26" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H26" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="J26" s="27"/>
-    </row>
-    <row r="27" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="B27" s="22" t="s">
-        <v>265</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="D27" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="F27" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="G27" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H27" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="J27" s="23"/>
-    </row>
-    <row r="28" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="B28" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="C28" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="D28" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="E28" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="F28" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="G28" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H28" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="J28" s="27"/>
-    </row>
-    <row r="29" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="B29" s="22" t="s">
-        <v>267</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="D29" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="F29" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="G29" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H29" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="J29" s="23" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="5"/>
-    </row>
-    <row r="31" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="B31" s="22" t="s">
-        <v>268</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="F31" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G31" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H31" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="J31" s="23"/>
-    </row>
-    <row r="32" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="B32" s="26" t="s">
-        <v>269</v>
-      </c>
-      <c r="C32" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="D32" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="E32" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="F32" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="G32" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H32" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I32" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="J32" s="27"/>
-    </row>
-    <row r="33" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="B33" s="22" t="s">
-        <v>270</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="F33" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="G33" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H33" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I33" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="J33" s="23"/>
-    </row>
-    <row r="34" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="B34" s="26" t="s">
-        <v>271</v>
-      </c>
-      <c r="C34" s="27" t="s">
-        <v>148</v>
-      </c>
-      <c r="D34" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="E34" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="F34" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="G34" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H34" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="J34" s="27"/>
-    </row>
-    <row r="35" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="20" t="s">
-        <v>298</v>
-      </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="5"/>
-    </row>
-    <row r="36" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="B36" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="D36" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="F36" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="G36" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H36" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I36" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="J36" s="23"/>
-    </row>
-    <row r="37" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="B37" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="C37" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="D37" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="E37" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="F37" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="G37" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H37" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I37" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="J37" s="27"/>
-    </row>
-    <row r="38" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="B38" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="C38" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="D38" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="E38" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="F38" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="G38" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H38" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I38" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="J38" s="23"/>
-    </row>
-    <row r="39" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="B39" s="26" t="s">
-        <v>275</v>
-      </c>
-      <c r="C39" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="D39" s="27" t="s">
-        <v>167</v>
-      </c>
-      <c r="E39" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="F39" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="G39" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="H39" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I39" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="J39" s="27"/>
-    </row>
-    <row r="40" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="B40" s="22" t="s">
-        <v>276</v>
-      </c>
-      <c r="C40" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="D40" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="E40" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="F40" s="23" t="s">
-        <v>173</v>
-      </c>
-      <c r="G40" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="H40" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I40" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="J40" s="23" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="20" t="s">
-        <v>300</v>
-      </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="5"/>
-    </row>
-    <row r="42" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="B42" s="22" t="s">
-        <v>277</v>
-      </c>
-      <c r="C42" s="23" t="s">
-        <v>176</v>
-      </c>
-      <c r="D42" s="23" t="s">
-        <v>177</v>
-      </c>
-      <c r="E42" s="23" t="s">
-        <v>178</v>
-      </c>
-      <c r="F42" s="23" t="s">
-        <v>179</v>
-      </c>
-      <c r="G42" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H42" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I42" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="J42" s="23" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="B43" s="26" t="s">
-        <v>278</v>
-      </c>
-      <c r="C43" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="D43" s="27" t="s">
-        <v>182</v>
-      </c>
-      <c r="E43" s="27" t="s">
-        <v>183</v>
-      </c>
-      <c r="F43" s="27" t="s">
-        <v>184</v>
-      </c>
-      <c r="G43" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H43" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I43" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="J43" s="27" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="B44" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="C44" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="D44" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="E44" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="F44" s="23" t="s">
-        <v>190</v>
-      </c>
-      <c r="G44" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H44" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I44" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="J44" s="23"/>
-    </row>
-    <row r="45" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="B45" s="26" t="s">
-        <v>280</v>
-      </c>
-      <c r="C45" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="D45" s="27" t="s">
-        <v>192</v>
-      </c>
-      <c r="E45" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="F45" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="G45" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="H45" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I45" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="J45" s="27"/>
-    </row>
-    <row r="46" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="5"/>
-    </row>
-    <row r="47" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="22" t="s">
-        <v>195</v>
-      </c>
-      <c r="B47" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="C47" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="D47" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="E47" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="F47" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="G47" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H47" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I47" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="J47" s="23"/>
-    </row>
-    <row r="48" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="B48" s="26" t="s">
-        <v>282</v>
-      </c>
-      <c r="C48" s="27" t="s">
-        <v>201</v>
-      </c>
-      <c r="D48" s="27" t="s">
-        <v>202</v>
-      </c>
-      <c r="E48" s="27" t="s">
-        <v>203</v>
-      </c>
-      <c r="F48" s="27" t="s">
-        <v>204</v>
-      </c>
-      <c r="G48" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H48" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I48" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="J48" s="27"/>
-    </row>
-    <row r="49" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="22" t="s">
-        <v>195</v>
-      </c>
-      <c r="B49" s="22" t="s">
-        <v>283</v>
-      </c>
-      <c r="C49" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="D49" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="E49" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="F49" s="23" t="s">
-        <v>208</v>
-      </c>
-      <c r="G49" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H49" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I49" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="J49" s="23"/>
-    </row>
-    <row r="50" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="B50" s="26" t="s">
-        <v>284</v>
-      </c>
-      <c r="C50" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="D50" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="E50" s="27" t="s">
-        <v>211</v>
-      </c>
-      <c r="F50" s="27" t="s">
-        <v>212</v>
-      </c>
-      <c r="G50" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H50" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I50" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="J50" s="27"/>
-    </row>
-    <row r="51" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="22" t="s">
-        <v>195</v>
-      </c>
-      <c r="B51" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="C51" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="D51" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="E51" s="23" t="s">
-        <v>215</v>
-      </c>
-      <c r="F51" s="23" t="s">
-        <v>216</v>
-      </c>
-      <c r="G51" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="H51" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I51" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="J51" s="23" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="B52" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="C52" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="D52" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="E52" s="27" t="s">
-        <v>220</v>
-      </c>
-      <c r="F52" s="27" t="s">
-        <v>221</v>
-      </c>
-      <c r="G52" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H52" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I52" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J52" s="27"/>
-    </row>
-    <row r="53" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="5"/>
-    </row>
-    <row r="54" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="B54" s="22" t="s">
-        <v>287</v>
-      </c>
-      <c r="C54" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="D54" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="E54" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="F54" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="G54" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H54" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I54" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="J54" s="23"/>
-    </row>
-    <row r="55" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="B55" s="26" t="s">
-        <v>288</v>
-      </c>
-      <c r="C55" s="27" t="s">
-        <v>225</v>
-      </c>
-      <c r="D55" s="27" t="s">
-        <v>226</v>
-      </c>
-      <c r="E55" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="F55" s="27" t="s">
-        <v>228</v>
-      </c>
-      <c r="G55" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H55" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I55" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="J55" s="27" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="B56" s="22" t="s">
-        <v>289</v>
-      </c>
-      <c r="C56" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="D56" s="23" t="s">
-        <v>232</v>
-      </c>
-      <c r="E56" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="F56" s="23" t="s">
-        <v>234</v>
-      </c>
-      <c r="G56" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H56" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I56" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="J56" s="23"/>
-    </row>
-    <row r="57" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="5"/>
-    </row>
-    <row r="58" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="B58" s="22" t="s">
-        <v>290</v>
-      </c>
-      <c r="C58" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="D58" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="E58" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="F58" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="G58" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H58" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I58" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="J58" s="23"/>
-    </row>
-    <row r="59" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="B59" s="26" t="s">
-        <v>291</v>
-      </c>
-      <c r="C59" s="27" t="s">
-        <v>241</v>
-      </c>
-      <c r="D59" s="27" t="s">
-        <v>242</v>
-      </c>
-      <c r="E59" s="27" t="s">
-        <v>243</v>
-      </c>
-      <c r="F59" s="27" t="s">
-        <v>244</v>
-      </c>
-      <c r="G59" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H59" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I59" s="26" t="s">
-        <v>240</v>
-      </c>
-      <c r="J59" s="27"/>
-    </row>
-    <row r="60" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="20" t="s">
-        <v>317</v>
-      </c>
-      <c r="B60" s="32"/>
-      <c r="C60" s="32"/>
-      <c r="D60" s="32"/>
-      <c r="E60" s="32"/>
-      <c r="F60" s="32"/>
-      <c r="G60" s="32"/>
-      <c r="H60" s="32"/>
-      <c r="I60" s="32"/>
-      <c r="J60" s="32"/>
-    </row>
-    <row r="61" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="22" t="s">
-        <v>303</v>
-      </c>
-      <c r="B61" s="22" t="s">
-        <v>314</v>
-      </c>
-      <c r="C61" s="23" t="s">
-        <v>304</v>
-      </c>
-      <c r="D61" s="23" t="s">
-        <v>305</v>
-      </c>
-      <c r="E61" s="23" t="s">
-        <v>306</v>
-      </c>
-      <c r="F61" s="23" t="s">
-        <v>307</v>
-      </c>
-      <c r="G61" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H61" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I61" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="J61" s="23" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="B62" s="26" t="s">
-        <v>315</v>
-      </c>
-      <c r="C62" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="D62" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="E62" s="27" t="s">
-        <v>311</v>
-      </c>
-      <c r="F62" s="27" t="s">
-        <v>312</v>
-      </c>
-      <c r="G62" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="H62" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I62" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="J62" s="27" t="s">
+      <c r="J62" s="36" t="s">
         <v>313</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A41:J41"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A53:J53"/>
+    <mergeCell ref="A57:J57"/>
     <mergeCell ref="A60:J60"/>
-    <mergeCell ref="A41:J41"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A46:J46"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A53:J53"/>
-    <mergeCell ref="A35:J35"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A57:J57"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test_plan.xlsx
+++ b/test_plan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OMEN\Documents\Eng. Raghad\DV\DV_project-claude-busy-turing-q1vwei\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OMEN\Documents\Eng. Raghad\DV\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD10F78B-B97A-40B6-BE31-1358EC5A83E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32F7E3AF-B659-40D8-895F-4B6E698061C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{2A3F12D1-36D3-4428-BC65-043ACAAD9E53}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="320">
   <si>
     <t>Electrical and Computer Engineering Department</t>
   </si>
@@ -985,7 +985,7 @@
     <t>Run</t>
   </si>
   <si>
-    <t>Run with error</t>
+    <t>DUT Bug</t>
   </si>
 </sst>
 </file>
@@ -1294,7 +1294,16 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1304,6 +1313,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1318,22 +1339,13 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1341,18 +1353,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1747,18 +1747,18 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
-      <c r="J3" s="20" t="s">
+      <c r="J3" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20"/>
-      <c r="P3" s="20"/>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="20"/>
-      <c r="S3" s="20"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
@@ -1781,16 +1781,16 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="20"/>
-      <c r="P4" s="20"/>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="20"/>
-      <c r="S4" s="20"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="23"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
@@ -1813,18 +1813,18 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="20" t="s">
+      <c r="J5" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="20"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
+      <c r="S5" s="23"/>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
@@ -1847,16 +1847,16 @@
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
-      <c r="N6" s="20"/>
-      <c r="O6" s="20"/>
-      <c r="P6" s="20"/>
-      <c r="Q6" s="20"/>
-      <c r="R6" s="20"/>
-      <c r="S6" s="20"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
+      <c r="S6" s="23"/>
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
@@ -1879,18 +1879,18 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="20" t="s">
+      <c r="J7" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="20"/>
-      <c r="P7" s="20"/>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="20"/>
-      <c r="S7" s="20"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
+      <c r="S7" s="23"/>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
@@ -1913,16 +1913,16 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="20"/>
-      <c r="N8" s="20"/>
-      <c r="O8" s="20"/>
-      <c r="P8" s="20"/>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="20"/>
-      <c r="S8" s="20"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="23"/>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
@@ -1945,18 +1945,18 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
-      <c r="J9" s="20" t="s">
+      <c r="J9" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="20"/>
-      <c r="S9" s="20"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
+      <c r="S9" s="23"/>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
@@ -2075,18 +2075,18 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="20" t="s">
+      <c r="J13" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="20"/>
-      <c r="O13" s="20"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="20"/>
-      <c r="S13" s="20"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
+      <c r="S13" s="23"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
@@ -2109,16 +2109,16 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
-      <c r="M14" s="20"/>
-      <c r="N14" s="20"/>
-      <c r="O14" s="20"/>
-      <c r="P14" s="20"/>
-      <c r="Q14" s="20"/>
-      <c r="R14" s="20"/>
-      <c r="S14" s="20"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
@@ -2141,18 +2141,18 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="20" t="s">
+      <c r="J15" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="20"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="20"/>
-      <c r="S15" s="20"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
@@ -2175,16 +2175,16 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="20"/>
-      <c r="P16" s="20"/>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="20"/>
-      <c r="S16" s="20"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="23"/>
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
@@ -2207,18 +2207,18 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="20" t="s">
+      <c r="J17" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="20"/>
-      <c r="P17" s="20"/>
-      <c r="Q17" s="20"/>
-      <c r="R17" s="20"/>
-      <c r="S17" s="20"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
+      <c r="S17" s="23"/>
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
@@ -2241,16 +2241,16 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-      <c r="M18" s="20"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
-      <c r="P18" s="20"/>
-      <c r="Q18" s="20"/>
-      <c r="R18" s="20"/>
-      <c r="S18" s="20"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
+      <c r="S18" s="23"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
@@ -2273,18 +2273,18 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="33" t="s">
+      <c r="J19" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="33"/>
-      <c r="N19" s="33"/>
-      <c r="O19" s="33"/>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="33"/>
-      <c r="R19" s="33"/>
-      <c r="S19" s="33"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="32"/>
+      <c r="N19" s="32"/>
+      <c r="O19" s="32"/>
+      <c r="P19" s="32"/>
+      <c r="Q19" s="32"/>
+      <c r="R19" s="32"/>
+      <c r="S19" s="32"/>
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
@@ -2307,16 +2307,16 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="33"/>
-      <c r="N20" s="33"/>
-      <c r="O20" s="33"/>
-      <c r="P20" s="33"/>
-      <c r="Q20" s="33"/>
-      <c r="R20" s="33"/>
-      <c r="S20" s="33"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="32"/>
+      <c r="R20" s="32"/>
+      <c r="S20" s="32"/>
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
@@ -2339,16 +2339,16 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
-      <c r="M21" s="33"/>
-      <c r="N21" s="33"/>
-      <c r="O21" s="33"/>
-      <c r="P21" s="33"/>
-      <c r="Q21" s="33"/>
-      <c r="R21" s="33"/>
-      <c r="S21" s="33"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="32"/>
+      <c r="O21" s="32"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="32"/>
+      <c r="S21" s="32"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
@@ -2371,16 +2371,16 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="33"/>
-      <c r="N22" s="33"/>
-      <c r="O22" s="33"/>
-      <c r="P22" s="33"/>
-      <c r="Q22" s="33"/>
-      <c r="R22" s="33"/>
-      <c r="S22" s="33"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="32"/>
+      <c r="N22" s="32"/>
+      <c r="O22" s="32"/>
+      <c r="P22" s="32"/>
+      <c r="Q22" s="32"/>
+      <c r="R22" s="32"/>
+      <c r="S22" s="32"/>
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
@@ -2531,18 +2531,18 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="20" t="s">
+      <c r="J27" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="20"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="20"/>
-      <c r="P27" s="20"/>
-      <c r="Q27" s="20"/>
-      <c r="R27" s="20"/>
-      <c r="S27" s="20"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
+      <c r="M27" s="23"/>
+      <c r="N27" s="23"/>
+      <c r="O27" s="23"/>
+      <c r="P27" s="23"/>
+      <c r="Q27" s="23"/>
+      <c r="R27" s="23"/>
+      <c r="S27" s="23"/>
       <c r="T27" s="1"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
@@ -2565,16 +2565,16 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="20"/>
-      <c r="P28" s="20"/>
-      <c r="Q28" s="20"/>
-      <c r="R28" s="20"/>
-      <c r="S28" s="20"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="23"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="23"/>
+      <c r="S28" s="23"/>
       <c r="T28" s="1"/>
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
@@ -2597,22 +2597,22 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="27" t="s">
+      <c r="J29" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="31"/>
-      <c r="N29" s="31"/>
-      <c r="O29" s="28"/>
-      <c r="P29" s="27" t="s">
+      <c r="K29" s="35"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
+      <c r="O29" s="25"/>
+      <c r="P29" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Q29" s="28"/>
-      <c r="R29" s="27" t="s">
+      <c r="Q29" s="25"/>
+      <c r="R29" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="S29" s="28"/>
+      <c r="S29" s="25"/>
       <c r="T29" s="1"/>
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
@@ -2635,16 +2635,16 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="29"/>
-      <c r="K30" s="32"/>
-      <c r="L30" s="32"/>
-      <c r="M30" s="32"/>
-      <c r="N30" s="32"/>
-      <c r="O30" s="30"/>
-      <c r="P30" s="29"/>
-      <c r="Q30" s="30"/>
-      <c r="R30" s="29"/>
-      <c r="S30" s="30"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="36"/>
+      <c r="M30" s="36"/>
+      <c r="N30" s="36"/>
+      <c r="O30" s="27"/>
+      <c r="P30" s="26"/>
+      <c r="Q30" s="27"/>
+      <c r="R30" s="26"/>
+      <c r="S30" s="27"/>
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
@@ -2667,22 +2667,22 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
-      <c r="J31" s="21" t="s">
+      <c r="J31" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="K31" s="25"/>
-      <c r="L31" s="25"/>
-      <c r="M31" s="25"/>
-      <c r="N31" s="25"/>
-      <c r="O31" s="22"/>
-      <c r="P31" s="21">
+      <c r="K31" s="33"/>
+      <c r="L31" s="33"/>
+      <c r="M31" s="33"/>
+      <c r="N31" s="33"/>
+      <c r="O31" s="29"/>
+      <c r="P31" s="28">
         <v>1191612</v>
       </c>
-      <c r="Q31" s="22"/>
-      <c r="R31" s="21">
+      <c r="Q31" s="29"/>
+      <c r="R31" s="28">
         <v>2</v>
       </c>
-      <c r="S31" s="22"/>
+      <c r="S31" s="29"/>
       <c r="T31" s="1"/>
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
@@ -2705,16 +2705,16 @@
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
-      <c r="J32" s="23"/>
-      <c r="K32" s="26"/>
-      <c r="L32" s="26"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="26"/>
-      <c r="O32" s="24"/>
-      <c r="P32" s="23"/>
-      <c r="Q32" s="24"/>
-      <c r="R32" s="23"/>
-      <c r="S32" s="24"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="34"/>
+      <c r="L32" s="34"/>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="31"/>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
@@ -2737,22 +2737,22 @@
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
-      <c r="J33" s="21" t="s">
+      <c r="J33" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="K33" s="25"/>
-      <c r="L33" s="25"/>
-      <c r="M33" s="25"/>
-      <c r="N33" s="25"/>
-      <c r="O33" s="22"/>
-      <c r="P33" s="21">
+      <c r="K33" s="33"/>
+      <c r="L33" s="33"/>
+      <c r="M33" s="33"/>
+      <c r="N33" s="33"/>
+      <c r="O33" s="29"/>
+      <c r="P33" s="28">
         <v>1212214</v>
       </c>
-      <c r="Q33" s="22"/>
-      <c r="R33" s="21">
+      <c r="Q33" s="29"/>
+      <c r="R33" s="28">
         <v>1</v>
       </c>
-      <c r="S33" s="22"/>
+      <c r="S33" s="29"/>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
@@ -2775,16 +2775,16 @@
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-      <c r="J34" s="23"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
-      <c r="M34" s="26"/>
-      <c r="N34" s="26"/>
-      <c r="O34" s="24"/>
-      <c r="P34" s="23"/>
-      <c r="Q34" s="24"/>
-      <c r="R34" s="23"/>
-      <c r="S34" s="24"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="34"/>
+      <c r="L34" s="34"/>
+      <c r="M34" s="34"/>
+      <c r="N34" s="34"/>
+      <c r="O34" s="31"/>
+      <c r="P34" s="30"/>
+      <c r="Q34" s="31"/>
+      <c r="R34" s="30"/>
+      <c r="S34" s="31"/>
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
@@ -2807,22 +2807,22 @@
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
-      <c r="J35" s="21" t="s">
+      <c r="J35" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="K35" s="25"/>
-      <c r="L35" s="25"/>
-      <c r="M35" s="25"/>
-      <c r="N35" s="25"/>
-      <c r="O35" s="22"/>
-      <c r="P35" s="21">
+      <c r="K35" s="33"/>
+      <c r="L35" s="33"/>
+      <c r="M35" s="33"/>
+      <c r="N35" s="33"/>
+      <c r="O35" s="29"/>
+      <c r="P35" s="28">
         <v>1221082</v>
       </c>
-      <c r="Q35" s="22"/>
-      <c r="R35" s="21">
+      <c r="Q35" s="29"/>
+      <c r="R35" s="28">
         <v>1</v>
       </c>
-      <c r="S35" s="22"/>
+      <c r="S35" s="29"/>
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
@@ -2845,16 +2845,16 @@
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
-      <c r="J36" s="23"/>
-      <c r="K36" s="26"/>
-      <c r="L36" s="26"/>
-      <c r="M36" s="26"/>
-      <c r="N36" s="26"/>
-      <c r="O36" s="24"/>
-      <c r="P36" s="23"/>
-      <c r="Q36" s="24"/>
-      <c r="R36" s="23"/>
-      <c r="S36" s="24"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="34"/>
+      <c r="L36" s="34"/>
+      <c r="M36" s="34"/>
+      <c r="N36" s="34"/>
+      <c r="O36" s="31"/>
+      <c r="P36" s="30"/>
+      <c r="Q36" s="31"/>
+      <c r="R36" s="30"/>
+      <c r="S36" s="31"/>
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
@@ -2877,22 +2877,22 @@
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
-      <c r="J37" s="21" t="s">
+      <c r="J37" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="K37" s="25"/>
-      <c r="L37" s="25"/>
-      <c r="M37" s="25"/>
-      <c r="N37" s="25"/>
-      <c r="O37" s="22"/>
-      <c r="P37" s="21">
+      <c r="K37" s="33"/>
+      <c r="L37" s="33"/>
+      <c r="M37" s="33"/>
+      <c r="N37" s="33"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="28">
         <v>1222275</v>
       </c>
-      <c r="Q37" s="22"/>
-      <c r="R37" s="21">
+      <c r="Q37" s="29"/>
+      <c r="R37" s="28">
         <v>2</v>
       </c>
-      <c r="S37" s="22"/>
+      <c r="S37" s="29"/>
       <c r="T37" s="3"/>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
@@ -2915,16 +2915,16 @@
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
-      <c r="J38" s="23"/>
-      <c r="K38" s="26"/>
-      <c r="L38" s="26"/>
-      <c r="M38" s="26"/>
-      <c r="N38" s="26"/>
-      <c r="O38" s="24"/>
-      <c r="P38" s="23"/>
-      <c r="Q38" s="24"/>
-      <c r="R38" s="23"/>
-      <c r="S38" s="24"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="34"/>
+      <c r="L38" s="34"/>
+      <c r="M38" s="34"/>
+      <c r="N38" s="34"/>
+      <c r="O38" s="31"/>
+      <c r="P38" s="30"/>
+      <c r="Q38" s="31"/>
+      <c r="R38" s="30"/>
+      <c r="S38" s="31"/>
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
@@ -3011,18 +3011,18 @@
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
-      <c r="J41" s="20" t="s">
+      <c r="J41" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="K41" s="20"/>
-      <c r="L41" s="20"/>
-      <c r="M41" s="20"/>
-      <c r="N41" s="20"/>
-      <c r="O41" s="20"/>
-      <c r="P41" s="20"/>
-      <c r="Q41" s="20"/>
-      <c r="R41" s="20"/>
-      <c r="S41" s="20"/>
+      <c r="K41" s="23"/>
+      <c r="L41" s="23"/>
+      <c r="M41" s="23"/>
+      <c r="N41" s="23"/>
+      <c r="O41" s="23"/>
+      <c r="P41" s="23"/>
+      <c r="Q41" s="23"/>
+      <c r="R41" s="23"/>
+      <c r="S41" s="23"/>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
@@ -3045,16 +3045,16 @@
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
-      <c r="J42" s="20"/>
-      <c r="K42" s="20"/>
-      <c r="L42" s="20"/>
-      <c r="M42" s="20"/>
-      <c r="N42" s="20"/>
-      <c r="O42" s="20"/>
-      <c r="P42" s="20"/>
-      <c r="Q42" s="20"/>
-      <c r="R42" s="20"/>
-      <c r="S42" s="20"/>
+      <c r="J42" s="23"/>
+      <c r="K42" s="23"/>
+      <c r="L42" s="23"/>
+      <c r="M42" s="23"/>
+      <c r="N42" s="23"/>
+      <c r="O42" s="23"/>
+      <c r="P42" s="23"/>
+      <c r="Q42" s="23"/>
+      <c r="R42" s="23"/>
+      <c r="S42" s="23"/>
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
@@ -3101,9 +3101,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="J17:S18"/>
-    <mergeCell ref="J19:S22"/>
-    <mergeCell ref="J27:S28"/>
     <mergeCell ref="J41:S42"/>
     <mergeCell ref="R35:S36"/>
     <mergeCell ref="J37:O38"/>
@@ -3117,15 +3114,18 @@
     <mergeCell ref="J35:O36"/>
     <mergeCell ref="P35:Q36"/>
     <mergeCell ref="P37:Q38"/>
-    <mergeCell ref="P29:Q30"/>
     <mergeCell ref="P31:Q32"/>
     <mergeCell ref="P33:Q34"/>
     <mergeCell ref="J5:S6"/>
     <mergeCell ref="J7:S8"/>
+    <mergeCell ref="J17:S18"/>
+    <mergeCell ref="J19:S22"/>
+    <mergeCell ref="J27:S28"/>
     <mergeCell ref="J3:S4"/>
     <mergeCell ref="J13:S14"/>
     <mergeCell ref="J15:S16"/>
     <mergeCell ref="J9:S9"/>
+    <mergeCell ref="P29:Q30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3133,7 +3133,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{758D3593-4783-47CC-8D9F-31D13BF080F4}">
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="20.7109375" customWidth="1"/>
@@ -3143,7 +3143,7 @@
     <col min="10" max="11" width="42.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>17</v>
       </c>
@@ -3171,25 +3171,25 @@
       <c r="I1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="34" t="s">
+      <c r="J1" s="17" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-    </row>
-    <row r="3" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+    </row>
+    <row r="3" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>26</v>
       </c>
@@ -3217,11 +3217,11 @@
       <c r="I3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="35" t="s">
+      <c r="J3" s="18" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>26</v>
       </c>
@@ -3249,9 +3249,9 @@
       <c r="I4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="36"/>
-    </row>
-    <row r="5" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J4" s="19"/>
+    </row>
+    <row r="5" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>26</v>
       </c>
@@ -3279,9 +3279,9 @@
       <c r="I5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="J5" s="35"/>
-    </row>
-    <row r="6" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J5" s="18"/>
+    </row>
+    <row r="6" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>26</v>
       </c>
@@ -3309,23 +3309,23 @@
       <c r="I6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="36"/>
-    </row>
-    <row r="7" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+      <c r="J6" s="19"/>
+    </row>
+    <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
         <v>294</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-    </row>
-    <row r="8" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+    </row>
+    <row r="8" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>47</v>
       </c>
@@ -3353,9 +3353,9 @@
       <c r="I8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="35"/>
-    </row>
-    <row r="9" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J8" s="18"/>
+    </row>
+    <row r="9" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>47</v>
       </c>
@@ -3383,9 +3383,9 @@
       <c r="I9" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="J9" s="36"/>
-    </row>
-    <row r="10" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J9" s="19"/>
+    </row>
+    <row r="10" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>47</v>
       </c>
@@ -3413,23 +3413,23 @@
       <c r="I10" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="35"/>
-    </row>
-    <row r="11" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="J10" s="18"/>
+    </row>
+    <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-    </row>
-    <row r="12" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+    </row>
+    <row r="12" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>63</v>
       </c>
@@ -3451,15 +3451,15 @@
       <c r="G12" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="8" t="s">
-        <v>32</v>
+      <c r="H12" s="15" t="s">
+        <v>318</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="J12" s="35"/>
-    </row>
-    <row r="13" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J12" s="18"/>
+    </row>
+    <row r="13" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>63</v>
       </c>
@@ -3481,15 +3481,15 @@
       <c r="G13" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="12" t="s">
-        <v>32</v>
+      <c r="H13" s="15" t="s">
+        <v>318</v>
       </c>
       <c r="I13" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="J13" s="36"/>
-    </row>
-    <row r="14" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J13" s="19"/>
+    </row>
+    <row r="14" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>63</v>
       </c>
@@ -3511,15 +3511,18 @@
       <c r="G14" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="8" t="s">
-        <v>32</v>
+      <c r="H14" s="15" t="s">
+        <v>318</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="J14" s="35"/>
-    </row>
-    <row r="15" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J14" s="18"/>
+      <c r="K14" s="20" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>63</v>
       </c>
@@ -3541,15 +3544,18 @@
       <c r="G15" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="12" t="s">
-        <v>32</v>
+      <c r="H15" s="15" t="s">
+        <v>318</v>
       </c>
       <c r="I15" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="J15" s="36"/>
-    </row>
-    <row r="16" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J15" s="19"/>
+      <c r="K15" s="20" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>63</v>
       </c>
@@ -3571,29 +3577,32 @@
       <c r="G16" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="H16" s="8" t="s">
-        <v>32</v>
+      <c r="H16" s="15" t="s">
+        <v>318</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="J16" s="35"/>
-    </row>
-    <row r="17" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+      <c r="J16" s="18"/>
+      <c r="K16" s="20" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-    </row>
-    <row r="18" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+    </row>
+    <row r="18" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>88</v>
       </c>
@@ -3621,9 +3630,9 @@
       <c r="I18" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="J18" s="35"/>
-    </row>
-    <row r="19" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J18" s="18"/>
+    </row>
+    <row r="19" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>88</v>
       </c>
@@ -3645,29 +3654,32 @@
       <c r="G19" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="H19" s="17" t="s">
-        <v>319</v>
+      <c r="H19" s="15" t="s">
+        <v>318</v>
       </c>
       <c r="I19" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="J19" s="36"/>
-    </row>
-    <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+      <c r="J19" s="19"/>
+      <c r="K19" s="20" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="21" t="s">
         <v>296</v>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-    </row>
-    <row r="21" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+    </row>
+    <row r="21" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>98</v>
       </c>
@@ -3695,11 +3707,11 @@
       <c r="I21" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="J21" s="35" t="s">
+      <c r="J21" s="18" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>98</v>
       </c>
@@ -3727,9 +3739,9 @@
       <c r="I22" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="J22" s="36"/>
-    </row>
-    <row r="23" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J22" s="19"/>
+    </row>
+    <row r="23" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>98</v>
       </c>
@@ -3757,9 +3769,9 @@
       <c r="I23" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="J23" s="35"/>
-    </row>
-    <row r="24" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J23" s="18"/>
+    </row>
+    <row r="24" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>98</v>
       </c>
@@ -3787,9 +3799,9 @@
       <c r="I24" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="J24" s="36"/>
-    </row>
-    <row r="25" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J24" s="19"/>
+    </row>
+    <row r="25" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>98</v>
       </c>
@@ -3817,9 +3829,9 @@
       <c r="I25" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="J25" s="35"/>
-    </row>
-    <row r="26" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>98</v>
       </c>
@@ -3847,9 +3859,9 @@
       <c r="I26" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="J26" s="36"/>
-    </row>
-    <row r="27" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J26" s="19"/>
+    </row>
+    <row r="27" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>98</v>
       </c>
@@ -3877,9 +3889,9 @@
       <c r="I27" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="J27" s="35"/>
-    </row>
-    <row r="28" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J27" s="18"/>
+    </row>
+    <row r="28" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>98</v>
       </c>
@@ -3907,9 +3919,9 @@
       <c r="I28" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="J28" s="36"/>
-    </row>
-    <row r="29" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J28" s="19"/>
+    </row>
+    <row r="29" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>98</v>
       </c>
@@ -3937,25 +3949,25 @@
       <c r="I29" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="J29" s="35" t="s">
+      <c r="J29" s="18" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="18" t="s">
+    <row r="30" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="21" t="s">
         <v>299</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-    </row>
-    <row r="31" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+    </row>
+    <row r="31" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>134</v>
       </c>
@@ -3983,9 +3995,9 @@
       <c r="I31" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="J31" s="35"/>
-    </row>
-    <row r="32" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J31" s="18"/>
+    </row>
+    <row r="32" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>134</v>
       </c>
@@ -4013,7 +4025,7 @@
       <c r="I32" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="J32" s="36"/>
+      <c r="J32" s="19"/>
     </row>
     <row r="33" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
@@ -4043,7 +4055,7 @@
       <c r="I33" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="J33" s="35"/>
+      <c r="J33" s="18"/>
     </row>
     <row r="34" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
@@ -4073,21 +4085,21 @@
       <c r="I34" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="J34" s="36"/>
+      <c r="J34" s="19"/>
     </row>
     <row r="35" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="21" t="s">
         <v>298</v>
       </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
     </row>
     <row r="36" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
@@ -4117,7 +4129,7 @@
       <c r="I36" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="J36" s="35"/>
+      <c r="J36" s="18"/>
     </row>
     <row r="37" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
@@ -4147,7 +4159,7 @@
       <c r="I37" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="J37" s="36"/>
+      <c r="J37" s="19"/>
     </row>
     <row r="38" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
@@ -4177,7 +4189,7 @@
       <c r="I38" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="J38" s="35"/>
+      <c r="J38" s="18"/>
     </row>
     <row r="39" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
@@ -4207,7 +4219,7 @@
       <c r="I39" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="J39" s="36"/>
+      <c r="J39" s="19"/>
     </row>
     <row r="40" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
@@ -4237,23 +4249,23 @@
       <c r="I40" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="J40" s="35" t="s">
+      <c r="J40" s="18" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="18" t="s">
+      <c r="A41" s="21" t="s">
         <v>300</v>
       </c>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
     </row>
     <row r="42" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
@@ -4283,7 +4295,7 @@
       <c r="I42" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="J42" s="35" t="s">
+      <c r="J42" s="18" t="s">
         <v>180</v>
       </c>
     </row>
@@ -4315,7 +4327,7 @@
       <c r="I43" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="J43" s="36" t="s">
+      <c r="J43" s="19" t="s">
         <v>186</v>
       </c>
     </row>
@@ -4347,7 +4359,7 @@
       <c r="I44" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="J44" s="35"/>
+      <c r="J44" s="18"/>
     </row>
     <row r="45" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
@@ -4377,21 +4389,21 @@
       <c r="I45" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="J45" s="36"/>
+      <c r="J45" s="19"/>
     </row>
     <row r="46" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="18" t="s">
+      <c r="A46" s="21" t="s">
         <v>316</v>
       </c>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="19"/>
-      <c r="J46" s="19"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="22"/>
+      <c r="H46" s="22"/>
+      <c r="I46" s="22"/>
+      <c r="J46" s="22"/>
     </row>
     <row r="47" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
@@ -4421,7 +4433,7 @@
       <c r="I47" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="J47" s="35"/>
+      <c r="J47" s="18"/>
     </row>
     <row r="48" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
@@ -4451,7 +4463,7 @@
       <c r="I48" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="J48" s="36"/>
+      <c r="J48" s="19"/>
     </row>
     <row r="49" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
@@ -4481,7 +4493,7 @@
       <c r="I49" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="J49" s="35"/>
+      <c r="J49" s="18"/>
     </row>
     <row r="50" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
@@ -4511,7 +4523,7 @@
       <c r="I50" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="J50" s="36"/>
+      <c r="J50" s="19"/>
     </row>
     <row r="51" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
@@ -4541,7 +4553,7 @@
       <c r="I51" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="J51" s="35" t="s">
+      <c r="J51" s="18" t="s">
         <v>217</v>
       </c>
     </row>
@@ -4573,21 +4585,21 @@
       <c r="I52" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="J52" s="36"/>
+      <c r="J52" s="19"/>
     </row>
     <row r="53" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="18" t="s">
+      <c r="A53" s="21" t="s">
         <v>301</v>
       </c>
-      <c r="B53" s="19"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="19"/>
-      <c r="E53" s="19"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="19"/>
-      <c r="I53" s="19"/>
-      <c r="J53" s="19"/>
+      <c r="B53" s="22"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
+      <c r="H53" s="22"/>
+      <c r="I53" s="22"/>
+      <c r="J53" s="22"/>
     </row>
     <row r="54" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
@@ -4617,7 +4629,7 @@
       <c r="I54" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="J54" s="35"/>
+      <c r="J54" s="18"/>
     </row>
     <row r="55" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
@@ -4647,7 +4659,7 @@
       <c r="I55" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="J55" s="36" t="s">
+      <c r="J55" s="19" t="s">
         <v>230</v>
       </c>
     </row>
@@ -4679,21 +4691,21 @@
       <c r="I56" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="J56" s="35"/>
+      <c r="J56" s="18"/>
     </row>
     <row r="57" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="18" t="s">
+      <c r="A57" s="21" t="s">
         <v>302</v>
       </c>
-      <c r="B57" s="19"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="19"/>
-      <c r="I57" s="19"/>
-      <c r="J57" s="19"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="22"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="22"/>
+      <c r="H57" s="22"/>
+      <c r="I57" s="22"/>
+      <c r="J57" s="22"/>
     </row>
     <row r="58" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
@@ -4723,7 +4735,7 @@
       <c r="I58" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="J58" s="35"/>
+      <c r="J58" s="18"/>
     </row>
     <row r="59" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
@@ -4753,21 +4765,21 @@
       <c r="I59" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="J59" s="36"/>
+      <c r="J59" s="19"/>
     </row>
     <row r="60" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="18" t="s">
+      <c r="A60" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="B60" s="19"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="19"/>
-      <c r="G60" s="19"/>
-      <c r="H60" s="19"/>
-      <c r="I60" s="19"/>
-      <c r="J60" s="19"/>
+      <c r="B60" s="22"/>
+      <c r="C60" s="22"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="22"/>
+      <c r="G60" s="22"/>
+      <c r="H60" s="22"/>
+      <c r="I60" s="22"/>
+      <c r="J60" s="22"/>
     </row>
     <row r="61" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
@@ -4797,7 +4809,7 @@
       <c r="I61" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="J61" s="35" t="s">
+      <c r="J61" s="18" t="s">
         <v>308</v>
       </c>
     </row>
@@ -4829,7 +4841,7 @@
       <c r="I62" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="J62" s="36" t="s">
+      <c r="J62" s="19" t="s">
         <v>313</v>
       </c>
     </row>
@@ -4840,13 +4852,13 @@
     <mergeCell ref="A11:J11"/>
     <mergeCell ref="A17:J17"/>
     <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A57:J57"/>
+    <mergeCell ref="A60:J60"/>
     <mergeCell ref="A30:J30"/>
     <mergeCell ref="A35:J35"/>
     <mergeCell ref="A41:J41"/>
     <mergeCell ref="A46:J46"/>
     <mergeCell ref="A53:J53"/>
-    <mergeCell ref="A57:J57"/>
-    <mergeCell ref="A60:J60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test_plan.xlsx
+++ b/test_plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OMEN\Documents\Eng. Raghad\DV\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32F7E3AF-B659-40D8-895F-4B6E698061C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31DDB8CF-6DEC-4A32-9307-B0E87B0DEF2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{2A3F12D1-36D3-4428-BC65-043ACAAD9E53}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="311">
   <si>
     <t>Electrical and Computer Engineering Department</t>
   </si>
@@ -124,15 +124,9 @@
     <t>High</t>
   </si>
   <si>
-    <t>Not Run</t>
-  </si>
-  <si>
     <t>Section 9</t>
   </si>
   <si>
-    <t>Active-low reset; check immediately on first negedge</t>
-  </si>
-  <si>
     <t>Reset During Local Packet</t>
   </si>
   <si>
@@ -340,9 +334,6 @@
     <t>Section 5</t>
   </si>
   <si>
-    <t>Baseline sanity check</t>
-  </si>
-  <si>
     <t>Valid cfg – Remote</t>
   </si>
   <si>
@@ -427,9 +418,6 @@
     <t>drop_cnt increments by 1; no local output</t>
   </si>
   <si>
-    <t>Per spec: FRAG_NUM shall equal 1 for local</t>
-  </si>
-  <si>
     <t>SEQ/FRAG</t>
   </si>
   <si>
@@ -550,9 +538,6 @@
     <t>All 31 fragments merged; new CRC16 correct</t>
   </si>
   <si>
-    <t>FRAG_NUM and SEQ_NUM up to 31</t>
-  </si>
-  <si>
     <t>CRC</t>
   </si>
   <si>
@@ -568,9 +553,6 @@
     <t>Last 2 bytes of data_local equal input CRC16 (unchanged)</t>
   </si>
   <si>
-    <t>CRC not recalculated for local traffic</t>
-  </si>
-  <si>
     <t>Remote CRC Regeneration</t>
   </si>
   <si>
@@ -586,9 +568,6 @@
     <t>Section 7.3</t>
   </si>
   <si>
-    <t>poly=0x1021, init=0xFFFF</t>
-  </si>
-  <si>
     <t>Remote CRC After Reordering</t>
   </si>
   <si>
@@ -679,9 +658,6 @@
     <t>drop_cnt = 0x0000</t>
   </si>
   <si>
-    <t>Send 65537 invalid packets</t>
-  </si>
-  <si>
     <t>Reset Clears Counter</t>
   </si>
   <si>
@@ -718,9 +694,6 @@
     <t>Sections 6–8</t>
   </si>
   <si>
-    <t>rand_test; use scoreboard</t>
-  </si>
-  <si>
     <t>Back-to-Back Remote Packets</t>
   </si>
   <si>
@@ -952,9 +925,6 @@
     <t>SEQ_NUM=1 packet dropped; drop_cnt increments by 1; SEQ_NUM=2 fragment handled per drop policy</t>
   </si>
   <si>
-    <t>Only one SEQ_NUM active at a time</t>
-  </si>
-  <si>
     <t>PAYLOAD_LEN &gt; 255 Not Possible</t>
   </si>
   <si>
@@ -967,9 +937,6 @@
     <t>PAYLOAD_LEN=255 accepted (no drop); PAYLOAD_LEN=0 causes drop and drop_cnt increments by 1</t>
   </si>
   <si>
-    <t>PAYLOAD_LEN is 8-bit → max=255. Values &gt;255 cannot be represented. Only boundary to test is 0 (invalid) and 255 (valid max).</t>
-  </si>
-  <si>
     <t>TP_REM_01</t>
   </si>
   <si>
@@ -982,17 +949,23 @@
     <t>ADDITIONAL CFG &amp; REMOTE VALIDATION</t>
   </si>
   <si>
-    <t>Run</t>
-  </si>
-  <si>
-    <t>DUT Bug</t>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>All 7 covergroups reach 100%</t>
+  </si>
+  <si>
+    <t>87.32% score; shortfall due to unreachable DUT paths</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1047,12 +1020,6 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF808080"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <color rgb="FFE36C09"/>
       <name val="Arial"/>
     </font>
@@ -1081,6 +1048,21 @@
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1247,8 +1229,8 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1267,9 +1249,6 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1279,32 +1258,23 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1313,6 +1283,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1327,31 +1315,25 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1747,18 +1729,18 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
-      <c r="J3" s="23" t="s">
+      <c r="J3" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="23"/>
-      <c r="O3" s="23"/>
-      <c r="P3" s="23"/>
-      <c r="Q3" s="23"/>
-      <c r="R3" s="23"/>
-      <c r="S3" s="23"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
@@ -1781,16 +1763,16 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
-      <c r="S4" s="23"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
@@ -1813,18 +1795,18 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="23" t="s">
+      <c r="J5" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
-      <c r="S5" s="23"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="19"/>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
@@ -1847,16 +1829,16 @@
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
-      <c r="S6" s="23"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
@@ -1879,18 +1861,18 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="23" t="s">
+      <c r="J7" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
       <c r="T7" s="1"/>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
@@ -1913,16 +1895,16 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="19"/>
+      <c r="S8" s="19"/>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
@@ -1945,18 +1927,18 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
-      <c r="J9" s="23" t="s">
+      <c r="J9" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="23"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
@@ -2075,18 +2057,18 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="23" t="s">
+      <c r="J13" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
@@ -2109,16 +2091,16 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
@@ -2141,18 +2123,18 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="23" t="s">
+      <c r="J15" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="23"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
-      <c r="S15" s="23"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="19"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
@@ -2175,16 +2157,16 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
-      <c r="S16" s="23"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
@@ -2207,18 +2189,18 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="23" t="s">
+      <c r="J17" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
-      <c r="S17" s="23"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="19"/>
+      <c r="R17" s="19"/>
+      <c r="S17" s="19"/>
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
@@ -2241,16 +2223,16 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
-      <c r="S18" s="23"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="19"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
@@ -2531,18 +2513,18 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="23" t="s">
+      <c r="J27" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="K27" s="23"/>
-      <c r="L27" s="23"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="23"/>
-      <c r="O27" s="23"/>
-      <c r="P27" s="23"/>
-      <c r="Q27" s="23"/>
-      <c r="R27" s="23"/>
-      <c r="S27" s="23"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
       <c r="T27" s="1"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
@@ -2565,16 +2547,16 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="23"/>
-      <c r="O28" s="23"/>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="23"/>
-      <c r="R28" s="23"/>
-      <c r="S28" s="23"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
       <c r="T28" s="1"/>
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
@@ -2597,22 +2579,22 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="24" t="s">
+      <c r="J29" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="K29" s="35"/>
-      <c r="L29" s="35"/>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
-      <c r="O29" s="25"/>
-      <c r="P29" s="24" t="s">
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="27"/>
+      <c r="P29" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="Q29" s="25"/>
-      <c r="R29" s="24" t="s">
+      <c r="Q29" s="27"/>
+      <c r="R29" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="S29" s="25"/>
+      <c r="S29" s="27"/>
       <c r="T29" s="1"/>
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
@@ -2635,16 +2617,16 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="36"/>
-      <c r="L30" s="36"/>
-      <c r="M30" s="36"/>
-      <c r="N30" s="36"/>
-      <c r="O30" s="27"/>
-      <c r="P30" s="26"/>
-      <c r="Q30" s="27"/>
-      <c r="R30" s="26"/>
-      <c r="S30" s="27"/>
+      <c r="J30" s="28"/>
+      <c r="K30" s="31"/>
+      <c r="L30" s="31"/>
+      <c r="M30" s="31"/>
+      <c r="N30" s="31"/>
+      <c r="O30" s="29"/>
+      <c r="P30" s="28"/>
+      <c r="Q30" s="29"/>
+      <c r="R30" s="28"/>
+      <c r="S30" s="29"/>
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
@@ -2667,22 +2649,22 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
-      <c r="J31" s="28" t="s">
+      <c r="J31" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="K31" s="33"/>
-      <c r="L31" s="33"/>
-      <c r="M31" s="33"/>
-      <c r="N31" s="33"/>
-      <c r="O31" s="29"/>
-      <c r="P31" s="28">
+      <c r="K31" s="24"/>
+      <c r="L31" s="24"/>
+      <c r="M31" s="24"/>
+      <c r="N31" s="24"/>
+      <c r="O31" s="21"/>
+      <c r="P31" s="20">
         <v>1191612</v>
       </c>
-      <c r="Q31" s="29"/>
-      <c r="R31" s="28">
+      <c r="Q31" s="21"/>
+      <c r="R31" s="20">
         <v>2</v>
       </c>
-      <c r="S31" s="29"/>
+      <c r="S31" s="21"/>
       <c r="T31" s="1"/>
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
@@ -2705,16 +2687,16 @@
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="34"/>
-      <c r="L32" s="34"/>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="30"/>
-      <c r="Q32" s="31"/>
-      <c r="R32" s="30"/>
-      <c r="S32" s="31"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
+      <c r="M32" s="25"/>
+      <c r="N32" s="25"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="23"/>
+      <c r="R32" s="22"/>
+      <c r="S32" s="23"/>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
@@ -2737,22 +2719,22 @@
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
-      <c r="J33" s="28" t="s">
+      <c r="J33" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="K33" s="33"/>
-      <c r="L33" s="33"/>
-      <c r="M33" s="33"/>
-      <c r="N33" s="33"/>
-      <c r="O33" s="29"/>
-      <c r="P33" s="28">
+      <c r="K33" s="24"/>
+      <c r="L33" s="24"/>
+      <c r="M33" s="24"/>
+      <c r="N33" s="24"/>
+      <c r="O33" s="21"/>
+      <c r="P33" s="20">
         <v>1212214</v>
       </c>
-      <c r="Q33" s="29"/>
-      <c r="R33" s="28">
+      <c r="Q33" s="21"/>
+      <c r="R33" s="20">
         <v>1</v>
       </c>
-      <c r="S33" s="29"/>
+      <c r="S33" s="21"/>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
@@ -2775,16 +2757,16 @@
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-      <c r="J34" s="30"/>
-      <c r="K34" s="34"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="34"/>
-      <c r="O34" s="31"/>
-      <c r="P34" s="30"/>
-      <c r="Q34" s="31"/>
-      <c r="R34" s="30"/>
-      <c r="S34" s="31"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
+      <c r="M34" s="25"/>
+      <c r="N34" s="25"/>
+      <c r="O34" s="23"/>
+      <c r="P34" s="22"/>
+      <c r="Q34" s="23"/>
+      <c r="R34" s="22"/>
+      <c r="S34" s="23"/>
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
@@ -2807,22 +2789,22 @@
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
-      <c r="J35" s="28" t="s">
+      <c r="J35" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="K35" s="33"/>
-      <c r="L35" s="33"/>
-      <c r="M35" s="33"/>
-      <c r="N35" s="33"/>
-      <c r="O35" s="29"/>
-      <c r="P35" s="28">
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="24"/>
+      <c r="N35" s="24"/>
+      <c r="O35" s="21"/>
+      <c r="P35" s="20">
         <v>1221082</v>
       </c>
-      <c r="Q35" s="29"/>
-      <c r="R35" s="28">
+      <c r="Q35" s="21"/>
+      <c r="R35" s="20">
         <v>1</v>
       </c>
-      <c r="S35" s="29"/>
+      <c r="S35" s="21"/>
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
@@ -2845,16 +2827,16 @@
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
-      <c r="J36" s="30"/>
-      <c r="K36" s="34"/>
-      <c r="L36" s="34"/>
-      <c r="M36" s="34"/>
-      <c r="N36" s="34"/>
-      <c r="O36" s="31"/>
-      <c r="P36" s="30"/>
-      <c r="Q36" s="31"/>
-      <c r="R36" s="30"/>
-      <c r="S36" s="31"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="25"/>
+      <c r="M36" s="25"/>
+      <c r="N36" s="25"/>
+      <c r="O36" s="23"/>
+      <c r="P36" s="22"/>
+      <c r="Q36" s="23"/>
+      <c r="R36" s="22"/>
+      <c r="S36" s="23"/>
       <c r="T36" s="3"/>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
@@ -2877,22 +2859,22 @@
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
-      <c r="J37" s="28" t="s">
+      <c r="J37" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="K37" s="33"/>
-      <c r="L37" s="33"/>
-      <c r="M37" s="33"/>
-      <c r="N37" s="33"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="28">
+      <c r="K37" s="24"/>
+      <c r="L37" s="24"/>
+      <c r="M37" s="24"/>
+      <c r="N37" s="24"/>
+      <c r="O37" s="21"/>
+      <c r="P37" s="20">
         <v>1222275</v>
       </c>
-      <c r="Q37" s="29"/>
-      <c r="R37" s="28">
+      <c r="Q37" s="21"/>
+      <c r="R37" s="20">
         <v>2</v>
       </c>
-      <c r="S37" s="29"/>
+      <c r="S37" s="21"/>
       <c r="T37" s="3"/>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
@@ -2915,16 +2897,16 @@
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
-      <c r="J38" s="30"/>
-      <c r="K38" s="34"/>
-      <c r="L38" s="34"/>
-      <c r="M38" s="34"/>
-      <c r="N38" s="34"/>
-      <c r="O38" s="31"/>
-      <c r="P38" s="30"/>
-      <c r="Q38" s="31"/>
-      <c r="R38" s="30"/>
-      <c r="S38" s="31"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="25"/>
+      <c r="L38" s="25"/>
+      <c r="M38" s="25"/>
+      <c r="N38" s="25"/>
+      <c r="O38" s="23"/>
+      <c r="P38" s="22"/>
+      <c r="Q38" s="23"/>
+      <c r="R38" s="22"/>
+      <c r="S38" s="23"/>
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
@@ -3011,18 +2993,18 @@
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
-      <c r="J41" s="23" t="s">
+      <c r="J41" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="K41" s="23"/>
-      <c r="L41" s="23"/>
-      <c r="M41" s="23"/>
-      <c r="N41" s="23"/>
-      <c r="O41" s="23"/>
-      <c r="P41" s="23"/>
-      <c r="Q41" s="23"/>
-      <c r="R41" s="23"/>
-      <c r="S41" s="23"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
+      <c r="N41" s="19"/>
+      <c r="O41" s="19"/>
+      <c r="P41" s="19"/>
+      <c r="Q41" s="19"/>
+      <c r="R41" s="19"/>
+      <c r="S41" s="19"/>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
@@ -3045,16 +3027,16 @@
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
-      <c r="J42" s="23"/>
-      <c r="K42" s="23"/>
-      <c r="L42" s="23"/>
-      <c r="M42" s="23"/>
-      <c r="N42" s="23"/>
-      <c r="O42" s="23"/>
-      <c r="P42" s="23"/>
-      <c r="Q42" s="23"/>
-      <c r="R42" s="23"/>
-      <c r="S42" s="23"/>
+      <c r="J42" s="19"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="19"/>
+      <c r="M42" s="19"/>
+      <c r="N42" s="19"/>
+      <c r="O42" s="19"/>
+      <c r="P42" s="19"/>
+      <c r="Q42" s="19"/>
+      <c r="R42" s="19"/>
+      <c r="S42" s="19"/>
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
@@ -3101,6 +3083,16 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="J3:S4"/>
+    <mergeCell ref="J13:S14"/>
+    <mergeCell ref="J15:S16"/>
+    <mergeCell ref="J9:S9"/>
+    <mergeCell ref="P29:Q30"/>
+    <mergeCell ref="J5:S6"/>
+    <mergeCell ref="J7:S8"/>
+    <mergeCell ref="J17:S18"/>
+    <mergeCell ref="J19:S22"/>
+    <mergeCell ref="J27:S28"/>
     <mergeCell ref="J41:S42"/>
     <mergeCell ref="R35:S36"/>
     <mergeCell ref="J37:O38"/>
@@ -3116,16 +3108,6 @@
     <mergeCell ref="P37:Q38"/>
     <mergeCell ref="P31:Q32"/>
     <mergeCell ref="P33:Q34"/>
-    <mergeCell ref="J5:S6"/>
-    <mergeCell ref="J7:S8"/>
-    <mergeCell ref="J17:S18"/>
-    <mergeCell ref="J19:S22"/>
-    <mergeCell ref="J27:S28"/>
-    <mergeCell ref="J3:S4"/>
-    <mergeCell ref="J13:S14"/>
-    <mergeCell ref="J15:S16"/>
-    <mergeCell ref="J9:S9"/>
-    <mergeCell ref="P29:Q30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3133,7 +3115,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{758D3593-4783-47CC-8D9F-31D13BF080F4}">
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="20.7109375" customWidth="1"/>
@@ -3143,12 +3125,12 @@
     <col min="10" max="11" width="42.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>18</v>
@@ -3171,35 +3153,35 @@
       <c r="I1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="36" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
-        <v>293</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-    </row>
-    <row r="3" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+    </row>
+    <row r="3" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E3" s="6" t="s">
@@ -3211,1647 +3193,1614 @@
       <c r="G3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="15" t="s">
-        <v>318</v>
+      <c r="H3" s="13" t="s">
+        <v>307</v>
       </c>
       <c r="I3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="6"/>
+    </row>
+    <row r="4" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="D4" s="9" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="C4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" s="19"/>
-    </row>
-    <row r="5" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H4" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="34"/>
+    </row>
+    <row r="5" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="15" t="s">
-        <v>318</v>
+      <c r="H5" s="13" t="s">
+        <v>307</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="J5" s="18"/>
-    </row>
-    <row r="6" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="F6" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="G6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="9"/>
+    </row>
+    <row r="7" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+    </row>
+    <row r="8" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="B8" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" s="19"/>
-    </row>
-    <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
-        <v>294</v>
-      </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-    </row>
-    <row r="8" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="E8" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>51</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H8" s="15" t="s">
-        <v>318</v>
+      <c r="H8" s="13" t="s">
+        <v>307</v>
       </c>
       <c r="I8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8" s="14"/>
+    </row>
+    <row r="9" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="18"/>
-    </row>
-    <row r="9" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="C9" s="10" t="s">
+      <c r="E9" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="F9" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="G9" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="J9" s="34"/>
+    </row>
+    <row r="10" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="G9" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="I9" s="9" t="s">
+      <c r="D10" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="J9" s="19"/>
-    </row>
-    <row r="10" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="C10" s="6" t="s">
+      <c r="E10" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="F10" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H10" s="15" t="s">
-        <v>318</v>
+      <c r="H10" s="13" t="s">
+        <v>307</v>
       </c>
       <c r="I10" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="J10" s="14"/>
+    </row>
+    <row r="11" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+    </row>
+    <row r="12" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="18"/>
-    </row>
-    <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>295</v>
-      </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-    </row>
-    <row r="12" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="C12" s="6" t="s">
+      <c r="E12" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="F12" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>67</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="15" t="s">
-        <v>318</v>
+      <c r="H12" s="13" t="s">
+        <v>307</v>
       </c>
       <c r="I12" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="J12" s="18"/>
-    </row>
-    <row r="13" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="C13" s="10" t="s">
+      <c r="E13" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="F13" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="G13" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="I13" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="J13" s="34"/>
+    </row>
+    <row r="14" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="G13" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="I13" s="9" t="s">
+      <c r="D14" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="J13" s="19"/>
-    </row>
-    <row r="14" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="C14" s="6" t="s">
+      <c r="E14" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="F14" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="15" t="s">
-        <v>318</v>
+      <c r="H14" s="33" t="s">
+        <v>308</v>
       </c>
       <c r="I14" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="J14" s="18"/>
-      <c r="K14" s="20" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C15" s="10" t="s">
+      <c r="E15" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="F15" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="G15" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="J15" s="34"/>
+    </row>
+    <row r="16" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="D16" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="G15" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="J15" s="19"/>
-      <c r="K15" s="20" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="C16" s="6" t="s">
+      <c r="E16" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="F16" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="G16" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="H16" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+    </row>
+    <row r="18" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="B18" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="H16" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="J16" s="18"/>
-      <c r="K16" s="20" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
-        <v>297</v>
-      </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-    </row>
-    <row r="18" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="D18" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="C18" s="6" t="s">
+      <c r="E18" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="F18" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>92</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="15" t="s">
-        <v>318</v>
+      <c r="H18" s="13" t="s">
+        <v>307</v>
       </c>
       <c r="I18" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="J18" s="18"/>
-    </row>
-    <row r="19" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="C19" s="10" t="s">
+      <c r="E19" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="F19" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="G19" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="J19" s="34"/>
+    </row>
+    <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+    </row>
+    <row r="21" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="B21" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="G19" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H19" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="J19" s="19"/>
-      <c r="K19" s="20" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
-        <v>296</v>
-      </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-    </row>
-    <row r="21" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+      <c r="D21" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="C21" s="6" t="s">
+      <c r="E21" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="F21" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="15" t="s">
-        <v>318</v>
+      <c r="H21" s="13" t="s">
+        <v>307</v>
       </c>
       <c r="I21" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="J21" s="18" t="s">
+      <c r="E22" s="9" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="C22" s="10" t="s">
+      <c r="F22" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="G22" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="J22" s="34"/>
+    </row>
+    <row r="23" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="D23" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="E23" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="G22" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H22" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="J22" s="19"/>
-    </row>
-    <row r="23" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="C23" s="6" t="s">
+      <c r="F23" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H23" s="15" t="s">
-        <v>318</v>
+      <c r="H23" s="13" t="s">
+        <v>307</v>
       </c>
       <c r="I23" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E24" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="J23" s="18"/>
-    </row>
-    <row r="24" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="C24" s="10" t="s">
+      <c r="F24" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="J24" s="34"/>
+    </row>
+    <row r="25" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D25" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E25" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="F24" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="G24" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H24" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="J24" s="19"/>
-    </row>
-    <row r="25" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>119</v>
-      </c>
       <c r="F25" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H25" s="15" t="s">
-        <v>318</v>
+      <c r="H25" s="13" t="s">
+        <v>307</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="J25" s="18"/>
-    </row>
-    <row r="26" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="C26" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="J26" s="34"/>
+    </row>
+    <row r="27" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D27" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E27" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="F26" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="G26" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H26" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="J26" s="19"/>
-    </row>
-    <row r="27" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>125</v>
-      </c>
       <c r="F27" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H27" s="15" t="s">
-        <v>318</v>
+      <c r="H27" s="13" t="s">
+        <v>307</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="J27" s="18"/>
-    </row>
-    <row r="28" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="C28" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="J28" s="34"/>
+    </row>
+    <row r="29" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D29" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E29" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="F28" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="G28" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H28" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="J28" s="19"/>
-    </row>
-    <row r="29" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="C29" s="6" t="s">
+      <c r="F29" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H29" s="15" t="s">
-        <v>318</v>
+      <c r="H29" s="13" t="s">
+        <v>307</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J29" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+    </row>
+    <row r="31" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E31" s="6" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="21" t="s">
-        <v>299</v>
-      </c>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
-    </row>
-    <row r="31" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
+      <c r="F31" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H31" s="8" t="s">
-        <v>32</v>
+      <c r="H31" s="33" t="s">
+        <v>308</v>
       </c>
       <c r="I31" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="J31" s="14"/>
+    </row>
+    <row r="32" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="F32" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="J31" s="18"/>
-    </row>
-    <row r="32" spans="1:11" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="G32" s="11" t="s">
+      <c r="G32" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="H32" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="J32" s="19"/>
+      <c r="H32" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="J32" s="14"/>
     </row>
     <row r="33" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G33" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H33" s="8" t="s">
-        <v>32</v>
+      <c r="H33" s="33" t="s">
+        <v>308</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="J33" s="18"/>
+        <v>110</v>
+      </c>
+      <c r="J33" s="14"/>
     </row>
     <row r="34" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="G34" s="11" t="s">
+      <c r="A34" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="G34" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="H34" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="J34" s="19"/>
+      <c r="H34" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="J34" s="14"/>
     </row>
     <row r="35" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="22"/>
+      <c r="A35" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="B35" s="18"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
     </row>
     <row r="36" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="F36" s="6" t="s">
         <v>152</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>156</v>
       </c>
       <c r="G36" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H36" s="8" t="s">
-        <v>32</v>
+      <c r="H36" s="33" t="s">
+        <v>308</v>
       </c>
       <c r="I36" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F37" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="J36" s="18"/>
-    </row>
-    <row r="37" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="G37" s="11" t="s">
+      <c r="G37" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="H37" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="J37" s="19"/>
+      <c r="H37" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="J37" s="14"/>
     </row>
     <row r="38" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G38" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H38" s="8" t="s">
-        <v>32</v>
+      <c r="H38" s="33" t="s">
+        <v>308</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="J38" s="18"/>
+        <v>153</v>
+      </c>
+      <c r="J38" s="14"/>
     </row>
     <row r="39" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="F39" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="G39" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="H39" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="J39" s="19"/>
+      <c r="A39" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H39" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="J39" s="34"/>
     </row>
     <row r="40" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="G40" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>32</v>
+        <v>169</v>
+      </c>
+      <c r="G40" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="H40" s="33" t="s">
+        <v>308</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="J40" s="18" t="s">
-        <v>174</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="J40" s="34"/>
     </row>
     <row r="41" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
-        <v>300</v>
-      </c>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="22"/>
+      <c r="A41" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
     </row>
     <row r="42" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G42" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H42" s="15" t="s">
-        <v>318</v>
+      <c r="H42" s="13" t="s">
+        <v>307</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J42" s="18" t="s">
-        <v>180</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J42" s="14"/>
     </row>
     <row r="43" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="C43" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="B43" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="F43" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="G43" s="11" t="s">
+      <c r="D43" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="H43" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="J43" s="19" t="s">
-        <v>186</v>
-      </c>
+      <c r="H43" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="J43" s="34"/>
     </row>
     <row r="44" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H44" s="15" t="s">
-        <v>318</v>
+      <c r="H44" s="13" t="s">
+        <v>307</v>
       </c>
       <c r="I44" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="J44" s="14"/>
+    </row>
+    <row r="45" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="D45" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="J44" s="18"/>
-    </row>
-    <row r="45" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="G45" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="H45" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="I45" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="J45" s="19"/>
+      <c r="E45" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H45" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="J45" s="34"/>
     </row>
     <row r="46" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="21" t="s">
-        <v>316</v>
-      </c>
-      <c r="B46" s="22"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="22"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="22"/>
-      <c r="H46" s="22"/>
-      <c r="I46" s="22"/>
-      <c r="J46" s="22"/>
+      <c r="A46" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="18"/>
     </row>
     <row r="47" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H47" s="15" t="s">
-        <v>318</v>
+      <c r="H47" s="13" t="s">
+        <v>307</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="J47" s="18"/>
+        <v>193</v>
+      </c>
+      <c r="J47" s="14"/>
     </row>
     <row r="48" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="9" t="s">
+      <c r="A48" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="D48" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="B48" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="F48" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="G48" s="11" t="s">
+      <c r="E48" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="G48" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="H48" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="I48" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="J48" s="19"/>
+      <c r="H48" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="J48" s="34"/>
     </row>
     <row r="49" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H49" s="15" t="s">
-        <v>318</v>
+      <c r="H49" s="13" t="s">
+        <v>307</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="J49" s="18"/>
+        <v>193</v>
+      </c>
+      <c r="J49" s="14"/>
     </row>
     <row r="50" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="F50" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="G50" s="11" t="s">
+      <c r="A50" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="G50" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="H50" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="I50" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="J50" s="19"/>
+      <c r="H50" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="J50" s="34"/>
     </row>
     <row r="51" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="C51" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="H51" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="J51" s="14"/>
+    </row>
+    <row r="52" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="F52" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="D51" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="G51" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="H51" s="8" t="s">
+      <c r="G52" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H52" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="I52" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="I51" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="J51" s="18" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="F52" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="G52" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H52" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="I52" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="J52" s="19"/>
+      <c r="J52" s="34"/>
     </row>
     <row r="53" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="21" t="s">
-        <v>301</v>
-      </c>
-      <c r="B53" s="22"/>
-      <c r="C53" s="22"/>
-      <c r="D53" s="22"/>
-      <c r="E53" s="22"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="22"/>
-      <c r="H53" s="22"/>
-      <c r="I53" s="22"/>
-      <c r="J53" s="22"/>
+      <c r="A53" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="B53" s="18"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="18"/>
     </row>
     <row r="54" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H54" s="8" t="s">
-        <v>32</v>
+      <c r="H54" s="13" t="s">
+        <v>307</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="J54" s="18"/>
+        <v>60</v>
+      </c>
+      <c r="J54" s="14"/>
     </row>
     <row r="55" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="F55" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="G55" s="11" t="s">
+      <c r="A55" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="G55" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="H55" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="I55" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="J55" s="19" t="s">
-        <v>230</v>
-      </c>
+      <c r="H55" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="J55" s="34"/>
     </row>
     <row r="56" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="C56" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="B56" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>231</v>
-      </c>
       <c r="D56" s="6" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H56" s="8" t="s">
-        <v>32</v>
+      <c r="H56" s="13" t="s">
+        <v>307</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J56" s="18"/>
+        <v>55</v>
+      </c>
+      <c r="J56" s="14"/>
     </row>
     <row r="57" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="B57" s="22"/>
-      <c r="C57" s="22"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="22"/>
-      <c r="H57" s="22"/>
-      <c r="I57" s="22"/>
-      <c r="J57" s="22"/>
+      <c r="A57" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
+      <c r="F57" s="18"/>
+      <c r="G57" s="18"/>
+      <c r="H57" s="18"/>
+      <c r="I57" s="18"/>
+      <c r="J57" s="18"/>
     </row>
     <row r="58" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H58" s="8" t="s">
-        <v>32</v>
+      <c r="H58" s="13" t="s">
+        <v>307</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="J58" s="18"/>
+        <v>231</v>
+      </c>
+      <c r="J58" s="15" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="59" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="9" t="s">
+      <c r="A59" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="F59" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="B59" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="C59" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="D59" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="F59" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="G59" s="11" t="s">
+      <c r="G59" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="H59" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="I59" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="J59" s="19"/>
+      <c r="H59" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="J59" s="16" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="60" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="21" t="s">
-        <v>317</v>
-      </c>
-      <c r="B60" s="22"/>
-      <c r="C60" s="22"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="22"/>
-      <c r="F60" s="22"/>
-      <c r="G60" s="22"/>
-      <c r="H60" s="22"/>
-      <c r="I60" s="22"/>
-      <c r="J60" s="22"/>
+      <c r="A60" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="18"/>
+      <c r="J60" s="18"/>
     </row>
     <row r="61" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B61" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="B61" s="5" t="s">
-        <v>314</v>
-      </c>
       <c r="C61" s="6" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="G61" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H61" s="8" t="s">
-        <v>32</v>
+      <c r="H61" s="33" t="s">
+        <v>308</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="J61" s="18" t="s">
-        <v>308</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="J61" s="35"/>
     </row>
     <row r="62" spans="1:10" ht="84.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B62" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="D62" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="E62" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="F62" s="10" t="s">
-        <v>312</v>
-      </c>
-      <c r="G62" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="H62" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="I62" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="J62" s="19" t="s">
-        <v>313</v>
-      </c>
+      <c r="A62" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="G62" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H62" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="J62" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A20:J20"/>
     <mergeCell ref="A57:J57"/>
     <mergeCell ref="A60:J60"/>
     <mergeCell ref="A30:J30"/>
@@ -4859,6 +4808,11 @@
     <mergeCell ref="A41:J41"/>
     <mergeCell ref="A46:J46"/>
     <mergeCell ref="A53:J53"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A20:J20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
